--- a/data/CRM_Journeys_Final_Updated_with_Type.xlsx
+++ b/data/CRM_Journeys_Final_Updated_with_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parithimalsaravanan/claude-projects/vfq/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7CE10D8-6CE8-DE4E-A9CA-DBEB5A95466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0862E6CA-26AE-144F-9FEC-27CA888C051B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page Type" sheetId="1" r:id="rId1"/>
@@ -3063,16 +3063,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3083,17 +3086,14 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3428,7 +3428,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3444,7 +3443,7 @@
     <col min="14" max="16384" width="8.83203125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3482,132 +3481,132 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="10">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>91</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="B4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
         <v>16</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="11"/>
-    </row>
-    <row r="3" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
-        <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>17</v>
@@ -3626,30 +3625,30 @@
       </c>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>14</v>
+        <v>55</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>18</v>
@@ -3658,70 +3657,70 @@
         <v>18</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>57</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>81</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>18</v>
@@ -3730,34 +3729,34 @@
         <v>18</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>20</v>
+        <v>83</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>18</v>
@@ -3766,34 +3765,34 @@
         <v>18</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>107</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>18</v>
@@ -3802,34 +3801,34 @@
         <v>18</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>111</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>18</v>
@@ -3838,34 +3837,34 @@
         <v>18</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>117</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>18</v>
@@ -3874,67 +3873,67 @@
         <v>18</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>132</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>20</v>
+        <v>136</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>17</v>
@@ -3946,25 +3945,25 @@
         <v>18</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>47</v>
+        <v>145</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>50</v>
@@ -3986,27 +3985,27 @@
       </c>
       <c r="L15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>20</v>
+        <v>149</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>17</v>
@@ -4018,25 +4017,25 @@
         <v>18</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L16" s="11"/>
     </row>
-    <row r="17" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>53</v>
+        <v>225</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>54</v>
+        <v>226</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>50</v>
@@ -4058,24 +4057,24 @@
       </c>
       <c r="L17" s="11"/>
     </row>
-    <row r="18" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>55</v>
+        <v>231</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>17</v>
@@ -4094,24 +4093,24 @@
       </c>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>57</v>
+        <v>238</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>58</v>
+        <v>239</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>17</v>
@@ -4123,28 +4122,28 @@
         <v>18</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L19" s="11"/>
     </row>
-    <row r="20" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>20</v>
+        <v>259</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>50</v>
@@ -4159,28 +4158,28 @@
         <v>18</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="10">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>20</v>
+        <v>261</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>62</v>
+        <v>262</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>50</v>
@@ -4195,28 +4194,28 @@
         <v>18</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L21" s="11"/>
     </row>
-    <row r="22" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>20</v>
+        <v>263</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>64</v>
+        <v>264</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>50</v>
@@ -4231,140 +4230,140 @@
         <v>18</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>20</v>
+        <v>265</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>67</v>
+        <v>266</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="11"/>
+    </row>
+    <row r="24" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="10">
+        <v>129</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="11"/>
+    </row>
+    <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="10">
+        <v>130</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="11"/>
-    </row>
-    <row r="24" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="11"/>
+    </row>
+    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
+        <v>149</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L25" s="11"/>
-    </row>
-    <row r="26" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="G26" s="10" t="s">
         <v>17</v>
       </c>
@@ -4382,30 +4381,30 @@
       </c>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>14</v>
+        <v>302</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>77</v>
+        <v>303</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I27" s="10" t="s">
         <v>18</v>
@@ -4414,34 +4413,34 @@
         <v>18</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>14</v>
+        <v>321</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>80</v>
+        <v>322</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I28" s="10" t="s">
         <v>18</v>
@@ -4454,21 +4453,21 @@
       </c>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>50</v>
@@ -4490,21 +4489,21 @@
       </c>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
-        <v>29</v>
+        <v>164</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>83</v>
+        <v>325</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>48</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>50</v>
@@ -4526,21 +4525,21 @@
       </c>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>20</v>
+        <v>327</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>86</v>
+        <v>328</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>50</v>
@@ -4562,176 +4561,174 @@
       </c>
       <c r="L31" s="11"/>
     </row>
-    <row r="32" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
+        <v>1</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>3</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33" s="11"/>
+    </row>
+    <row r="34" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>5</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>6</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10">
+      <c r="D35" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10">
+      <c r="F35" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="11"/>
+    </row>
+    <row r="36" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>7</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L34" s="11"/>
-    </row>
-    <row r="35" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10">
+      <c r="D36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="11"/>
-    </row>
-    <row r="36" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10">
-        <v>35</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="F36" s="11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>18</v>
@@ -4740,34 +4737,34 @@
         <v>18</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L36" s="11"/>
     </row>
-    <row r="37" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>18</v>
@@ -4776,28 +4773,28 @@
         <v>18</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L37" s="11"/>
     </row>
-    <row r="38" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>20</v>
+        <v>39</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>17</v>
@@ -4812,34 +4809,34 @@
         <v>18</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L38" s="11"/>
     </row>
-    <row r="39" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>20</v>
+        <v>41</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="10" t="s">
         <v>18</v>
@@ -4848,70 +4845,70 @@
         <v>18</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L39" s="11"/>
     </row>
-    <row r="40" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>20</v>
+        <v>43</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I40" s="10" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K40" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L40" s="11"/>
     </row>
-    <row r="41" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>18</v>
@@ -4920,34 +4917,34 @@
         <v>18</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L41" s="11"/>
     </row>
-    <row r="42" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>20</v>
+        <v>79</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>18</v>
@@ -4960,33 +4957,33 @@
       </c>
       <c r="L42" s="11"/>
     </row>
-    <row r="43" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>48</v>
+        <v>119</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>18</v>
@@ -4994,32 +4991,34 @@
       <c r="K43" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L43" s="11"/>
-    </row>
-    <row r="44" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L43" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>20</v>
+        <v>124</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>18</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>115</v>
@@ -5028,57 +5027,59 @@
         <v>18</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="10">
         <v>48</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L45" s="11"/>
-    </row>
-    <row r="46" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="10">
-        <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>120</v>
@@ -5090,13 +5091,13 @@
         <v>122</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="J46" s="10" t="s">
         <v>18</v>
@@ -5104,19 +5105,17 @@
       <c r="K46" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L46" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L46" s="11"/>
+    </row>
+    <row r="47" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>120</v>
@@ -5128,13 +5127,13 @@
         <v>122</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="J47" s="10" t="s">
         <v>18</v>
@@ -5142,19 +5141,17 @@
       <c r="K47" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L47" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L47" s="11"/>
+    </row>
+    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>120</v>
@@ -5166,33 +5163,31 @@
         <v>122</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K48" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L48" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L48" s="11"/>
+    </row>
+    <row r="49" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>120</v>
@@ -5220,15 +5215,15 @@
       </c>
       <c r="L49" s="11"/>
     </row>
-    <row r="50" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>120</v>
@@ -5256,24 +5251,24 @@
       </c>
       <c r="L50" s="11"/>
     </row>
-    <row r="51" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>20</v>
+        <v>157</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>17</v>
@@ -5290,28 +5285,26 @@
       <c r="K51" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L51" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L51" s="11"/>
+    </row>
+    <row r="52" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>48</v>
+        <v>160</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>17</v>
@@ -5330,24 +5323,24 @@
       </c>
       <c r="L52" s="11"/>
     </row>
-    <row r="53" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>20</v>
+        <v>164</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>17</v>
@@ -5366,24 +5359,24 @@
       </c>
       <c r="L53" s="11"/>
     </row>
-    <row r="54" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>48</v>
+        <v>175</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>17</v>
@@ -5402,24 +5395,24 @@
       </c>
       <c r="L54" s="11"/>
     </row>
-    <row r="55" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>20</v>
+        <v>176</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>17</v>
@@ -5438,15 +5431,15 @@
       </c>
       <c r="L55" s="11"/>
     </row>
-    <row r="56" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>120</v>
@@ -5467,31 +5460,31 @@
         <v>18</v>
       </c>
       <c r="J56" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L56" s="11"/>
     </row>
-    <row r="57" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>20</v>
+        <v>185</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>17</v>
@@ -5510,24 +5503,24 @@
       </c>
       <c r="L57" s="11"/>
     </row>
-    <row r="58" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="10">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>20</v>
+        <v>186</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>17</v>
@@ -5539,31 +5532,31 @@
         <v>18</v>
       </c>
       <c r="J58" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K58" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L58" s="11"/>
     </row>
-    <row r="59" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="10">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>48</v>
+        <v>187</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>17</v>
@@ -5582,24 +5575,24 @@
       </c>
       <c r="L59" s="11"/>
     </row>
-    <row r="60" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="10">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>20</v>
+        <v>192</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>17</v>
@@ -5618,24 +5611,24 @@
       </c>
       <c r="L60" s="11"/>
     </row>
-    <row r="61" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="10">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>48</v>
+        <v>193</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>17</v>
@@ -5654,15 +5647,15 @@
       </c>
       <c r="L61" s="11"/>
     </row>
-    <row r="62" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="10">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>120</v>
@@ -5690,24 +5683,24 @@
       </c>
       <c r="L62" s="11"/>
     </row>
-    <row r="63" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="10">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>20</v>
+        <v>200</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>17</v>
@@ -5719,31 +5712,31 @@
         <v>18</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K63" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L63" s="11"/>
     </row>
-    <row r="64" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="10">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>20</v>
+        <v>201</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>17</v>
@@ -5755,28 +5748,28 @@
         <v>18</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K64" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L64" s="11"/>
     </row>
-    <row r="65" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="10">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="D65" s="7" t="s">
         <v>120</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="F65" s="11" t="s">
         <v>122</v>
@@ -5798,21 +5791,21 @@
       </c>
       <c r="L65" s="11"/>
     </row>
-    <row r="66" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="10">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>120</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>121</v>
+        <v>215</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>122</v>
@@ -5830,28 +5823,28 @@
         <v>18</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L66" s="11"/>
     </row>
-    <row r="67" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="10">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>20</v>
+        <v>229</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>17</v>
@@ -5870,15 +5863,15 @@
       </c>
       <c r="L67" s="11"/>
     </row>
-    <row r="68" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="10">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>160</v>
+        <v>278</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>120</v>
@@ -5902,25 +5895,25 @@
         <v>18</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L68" s="11"/>
     </row>
-    <row r="69" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="10">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>162</v>
+        <v>295</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>122</v>
@@ -5935,28 +5928,28 @@
         <v>18</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L69" s="11"/>
     </row>
-    <row r="70" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="10">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>164</v>
+        <v>300</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>120</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="F70" s="11" t="s">
         <v>122</v>
@@ -5978,24 +5971,24 @@
       </c>
       <c r="L70" s="11"/>
     </row>
-    <row r="71" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="10">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>20</v>
+        <v>305</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>17</v>
@@ -6014,27 +6007,27 @@
       </c>
       <c r="L71" s="11"/>
     </row>
-    <row r="72" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="10">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>18</v>
@@ -6046,28 +6039,28 @@
         <v>18</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L72" s="11"/>
     </row>
-    <row r="73" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="10">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>171</v>
+        <v>25</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>17</v>
@@ -6082,34 +6075,34 @@
         <v>18</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L73" s="11"/>
     </row>
-    <row r="74" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="10">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>18</v>
@@ -6122,27 +6115,27 @@
       </c>
       <c r="L74" s="11"/>
     </row>
-    <row r="75" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="10">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>120</v>
+        <v>45</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>17</v>
@@ -6154,31 +6147,31 @@
         <v>18</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L75" s="11"/>
     </row>
-    <row r="76" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="10">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>120</v>
+        <v>51</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>17</v>
@@ -6190,25 +6183,25 @@
         <v>18</v>
       </c>
       <c r="K76" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L76" s="11"/>
     </row>
-    <row r="77" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A77" s="10">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>50</v>
@@ -6223,28 +6216,28 @@
         <v>18</v>
       </c>
       <c r="J77" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L77" s="11"/>
     </row>
-    <row r="78" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="10">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>50</v>
@@ -6259,31 +6252,31 @@
         <v>18</v>
       </c>
       <c r="J78" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K78" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L78" s="11"/>
     </row>
-    <row r="79" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" s="10">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>120</v>
+        <v>63</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>17</v>
@@ -6295,31 +6288,31 @@
         <v>18</v>
       </c>
       <c r="J79" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K79" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L79" s="11"/>
     </row>
-    <row r="80" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="10">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>17</v>
@@ -6334,28 +6327,28 @@
         <v>18</v>
       </c>
       <c r="K80" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L80" s="11"/>
     </row>
-    <row r="81" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="10">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>120</v>
+        <v>68</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>17</v>
@@ -6367,31 +6360,31 @@
         <v>18</v>
       </c>
       <c r="J81" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L81" s="11"/>
     </row>
-    <row r="82" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="10">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>120</v>
+        <v>70</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>17</v>
@@ -6410,24 +6403,24 @@
       </c>
       <c r="L82" s="11"/>
     </row>
-    <row r="83" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="10">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>120</v>
+        <v>73</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>17</v>
@@ -6446,21 +6439,21 @@
       </c>
       <c r="L83" s="11"/>
     </row>
-    <row r="84" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="10">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>50</v>
@@ -6478,25 +6471,25 @@
         <v>18</v>
       </c>
       <c r="K84" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L84" s="11"/>
     </row>
-    <row r="85" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="10">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="F85" s="11" t="s">
         <v>50</v>
@@ -6511,28 +6504,30 @@
         <v>18</v>
       </c>
       <c r="J85" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L85" s="11"/>
-    </row>
-    <row r="86" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L85" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="10">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>189</v>
+        <v>91</v>
       </c>
       <c r="F86" s="11" t="s">
         <v>50</v>
@@ -6554,24 +6549,24 @@
       </c>
       <c r="L86" s="11"/>
     </row>
-    <row r="87" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="10">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>120</v>
+        <v>92</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G87" s="10" t="s">
         <v>17</v>
@@ -6590,24 +6585,24 @@
       </c>
       <c r="L87" s="11"/>
     </row>
-    <row r="88" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="10">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>120</v>
+        <v>94</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G88" s="10" t="s">
         <v>17</v>
@@ -6619,31 +6614,31 @@
         <v>18</v>
       </c>
       <c r="J88" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K88" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L88" s="11"/>
     </row>
-    <row r="89" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="10">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>120</v>
+        <v>96</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G89" s="10" t="s">
         <v>17</v>
@@ -6662,21 +6657,21 @@
       </c>
       <c r="L89" s="11"/>
     </row>
-    <row r="90" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="10">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>195</v>
+        <v>98</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>50</v>
@@ -6694,34 +6689,34 @@
         <v>18</v>
       </c>
       <c r="K90" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L90" s="11"/>
     </row>
-    <row r="91" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A91" s="10">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>197</v>
+        <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="G91" s="10" t="s">
         <v>17</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" s="10" t="s">
         <v>18</v>
@@ -6734,24 +6729,24 @@
       </c>
       <c r="L91" s="11"/>
     </row>
-    <row r="92" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="10">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>162</v>
+        <v>103</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G92" s="10" t="s">
         <v>17</v>
@@ -6766,28 +6761,28 @@
         <v>18</v>
       </c>
       <c r="K92" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L92" s="11"/>
     </row>
-    <row r="93" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="10">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>120</v>
+        <v>105</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G93" s="10" t="s">
         <v>17</v>
@@ -6806,24 +6801,24 @@
       </c>
       <c r="L93" s="11"/>
     </row>
-    <row r="94" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="10">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G94" s="10" t="s">
         <v>17</v>
@@ -6842,57 +6837,59 @@
       </c>
       <c r="L94" s="11"/>
     </row>
-    <row r="95" spans="1:12" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A95" s="10">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>202</v>
+        <v>113</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F95" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="I95" s="10" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="J95" s="10" t="s">
         <v>18</v>
       </c>
       <c r="K95" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="L95" s="11"/>
-    </row>
-    <row r="96" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="L95" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" s="10">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="F96" s="11" t="s">
         <v>50</v>
@@ -6912,23 +6909,25 @@
       <c r="K96" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L96" s="11"/>
-    </row>
-    <row r="97" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L96" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="F97" s="11" t="s">
         <v>50</v>
@@ -6950,24 +6949,24 @@
       </c>
       <c r="L97" s="11"/>
     </row>
-    <row r="98" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="10">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>120</v>
+        <v>138</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G98" s="10" t="s">
         <v>17</v>
@@ -6986,21 +6985,21 @@
       </c>
       <c r="L98" s="11"/>
     </row>
-    <row r="99" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" s="10">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>210</v>
+        <v>141</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="F99" s="11" t="s">
         <v>50</v>
@@ -7022,21 +7021,21 @@
       </c>
       <c r="L99" s="11"/>
     </row>
-    <row r="100" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A100" s="10">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="F100" s="11" t="s">
         <v>50</v>
@@ -7051,31 +7050,31 @@
         <v>18</v>
       </c>
       <c r="J100" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L100" s="11"/>
     </row>
-    <row r="101" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="10">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>120</v>
+        <v>147</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>215</v>
+        <v>148</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>17</v>
@@ -7090,25 +7089,25 @@
         <v>18</v>
       </c>
       <c r="K101" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L101" s="11"/>
     </row>
-    <row r="102" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="10">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>217</v>
+        <v>152</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="F102" s="11" t="s">
         <v>50</v>
@@ -7123,28 +7122,28 @@
         <v>18</v>
       </c>
       <c r="J102" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K102" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L102" s="11"/>
     </row>
-    <row r="103" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A103" s="10">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>220</v>
+        <v>155</v>
       </c>
       <c r="F103" s="11" t="s">
         <v>50</v>
@@ -7159,28 +7158,28 @@
         <v>18</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L103" s="11"/>
     </row>
-    <row r="104" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" s="10">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>222</v>
+        <v>159</v>
       </c>
       <c r="F104" s="11" t="s">
         <v>50</v>
@@ -7198,28 +7197,28 @@
         <v>18</v>
       </c>
       <c r="K104" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L104" s="11"/>
     </row>
-    <row r="105" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="10">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="G105" s="10" t="s">
         <v>17</v>
@@ -7238,30 +7237,30 @@
       </c>
       <c r="L105" s="11"/>
     </row>
-    <row r="106" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A106" s="10">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>48</v>
+        <v>169</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" s="10" t="s">
         <v>18</v>
@@ -7274,21 +7273,21 @@
       </c>
       <c r="L106" s="11"/>
     </row>
-    <row r="107" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="10">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="F107" s="11" t="s">
         <v>50</v>
@@ -7306,25 +7305,25 @@
         <v>18</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L107" s="11"/>
     </row>
-    <row r="108" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="10">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F108" s="11" t="s">
         <v>50</v>
@@ -7342,28 +7341,28 @@
         <v>18</v>
       </c>
       <c r="K108" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L108" s="11"/>
     </row>
-    <row r="109" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="10">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>120</v>
+        <v>177</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G109" s="10" t="s">
         <v>17</v>
@@ -7382,24 +7381,24 @@
       </c>
       <c r="L109" s="11"/>
     </row>
-    <row r="110" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="10">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>48</v>
+        <v>179</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G110" s="10" t="s">
         <v>17</v>
@@ -7414,28 +7413,28 @@
         <v>18</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L110" s="11"/>
     </row>
-    <row r="111" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="10">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="G111" s="10" t="s">
         <v>17</v>
@@ -7450,19 +7449,19 @@
         <v>18</v>
       </c>
       <c r="K111" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L111" s="11"/>
     </row>
-    <row r="112" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="10">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>20</v>
@@ -7486,19 +7485,19 @@
         <v>18</v>
       </c>
       <c r="K112" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L112" s="11"/>
     </row>
-    <row r="113" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="10">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>20</v>
@@ -7519,22 +7518,22 @@
         <v>18</v>
       </c>
       <c r="J113" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K113" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L113" s="11"/>
     </row>
-    <row r="114" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="10">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>20</v>
@@ -7562,24 +7561,24 @@
       </c>
       <c r="L114" s="11"/>
     </row>
-    <row r="115" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" s="10">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>48</v>
+        <v>195</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G115" s="10" t="s">
         <v>17</v>
@@ -7594,28 +7593,28 @@
         <v>18</v>
       </c>
       <c r="K115" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L115" s="11"/>
     </row>
-    <row r="116" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A116" s="10">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G116" s="10" t="s">
         <v>17</v>
@@ -7634,24 +7633,24 @@
       </c>
       <c r="L116" s="11"/>
     </row>
-    <row r="117" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="80" x14ac:dyDescent="0.2">
       <c r="A117" s="10">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>243</v>
+        <v>50</v>
       </c>
       <c r="G117" s="10" t="s">
         <v>17</v>
@@ -7666,25 +7665,25 @@
         <v>18</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L117" s="11"/>
     </row>
-    <row r="118" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A118" s="10">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="F118" s="11" t="s">
         <v>50</v>
@@ -7706,21 +7705,21 @@
       </c>
       <c r="L118" s="11"/>
     </row>
-    <row r="119" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A119" s="10">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="F119" s="11" t="s">
         <v>50</v>
@@ -7738,25 +7737,25 @@
         <v>18</v>
       </c>
       <c r="K119" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L119" s="11"/>
     </row>
-    <row r="120" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A120" s="10">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="F120" s="11" t="s">
         <v>50</v>
@@ -7778,21 +7777,21 @@
       </c>
       <c r="L120" s="11"/>
     </row>
-    <row r="121" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" s="10">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="F121" s="11" t="s">
         <v>50</v>
@@ -7807,28 +7806,28 @@
         <v>18</v>
       </c>
       <c r="J121" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K121" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L121" s="11"/>
     </row>
-    <row r="122" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A122" s="10">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>253</v>
+        <v>218</v>
       </c>
       <c r="F122" s="11" t="s">
         <v>50</v>
@@ -7843,28 +7842,28 @@
         <v>18</v>
       </c>
       <c r="J122" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K122" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L122" s="11"/>
     </row>
-    <row r="123" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A123" s="10">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="F123" s="11" t="s">
         <v>50</v>
@@ -7886,21 +7885,21 @@
       </c>
       <c r="L123" s="11"/>
     </row>
-    <row r="124" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A124" s="10">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="F124" s="11" t="s">
         <v>50</v>
@@ -7922,21 +7921,21 @@
       </c>
       <c r="L124" s="11"/>
     </row>
-    <row r="125" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A125" s="10">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="F125" s="11" t="s">
         <v>50</v>
@@ -7958,21 +7957,21 @@
       </c>
       <c r="L125" s="11"/>
     </row>
-    <row r="126" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="10">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>48</v>
+        <v>227</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="F126" s="11" t="s">
         <v>50</v>
@@ -7994,21 +7993,21 @@
       </c>
       <c r="L126" s="11"/>
     </row>
-    <row r="127" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="10">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>48</v>
+        <v>228</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="F127" s="11" t="s">
         <v>50</v>
@@ -8030,24 +8029,24 @@
       </c>
       <c r="L127" s="11"/>
     </row>
-    <row r="128" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="10">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>48</v>
+        <v>233</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="G128" s="10" t="s">
         <v>17</v>
@@ -8066,24 +8065,24 @@
       </c>
       <c r="L128" s="11"/>
     </row>
-    <row r="129" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A129" s="10">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>48</v>
+        <v>235</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>266</v>
+        <v>50</v>
       </c>
       <c r="G129" s="10" t="s">
         <v>17</v>
@@ -8102,24 +8101,24 @@
       </c>
       <c r="L129" s="11"/>
     </row>
-    <row r="130" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="10">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>48</v>
+        <v>236</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>266</v>
+        <v>50</v>
       </c>
       <c r="G130" s="10" t="s">
         <v>17</v>
@@ -8138,21 +8137,21 @@
       </c>
       <c r="L130" s="11"/>
     </row>
-    <row r="131" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="10">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>48</v>
+        <v>237</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
       <c r="F131" s="11" t="s">
         <v>50</v>
@@ -8174,21 +8173,21 @@
       </c>
       <c r="L131" s="11"/>
     </row>
-    <row r="132" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="10">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B132" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="F132" s="11" t="s">
         <v>50</v>
@@ -8210,24 +8209,24 @@
       </c>
       <c r="L132" s="11"/>
     </row>
-    <row r="133" spans="1:12" ht="80" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="10">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>50</v>
+        <v>243</v>
       </c>
       <c r="G133" s="10" t="s">
         <v>17</v>
@@ -8246,21 +8245,21 @@
       </c>
       <c r="L133" s="11"/>
     </row>
-    <row r="134" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" s="10">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="F134" s="11" t="s">
         <v>50</v>
@@ -8275,28 +8274,28 @@
         <v>18</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K134" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L134" s="11"/>
     </row>
-    <row r="135" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="10">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="F135" s="11" t="s">
         <v>50</v>
@@ -8318,57 +8317,57 @@
       </c>
       <c r="L135" s="11"/>
     </row>
-    <row r="136" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="10">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="D136" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J136" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K136" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L136" s="11"/>
+    </row>
+    <row r="137" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A137" s="10">
         <v>120</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F136" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H136" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I136" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J136" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="K136" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L136" s="11"/>
-    </row>
-    <row r="137" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="10">
-        <v>136</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>50</v>
@@ -8383,28 +8382,28 @@
         <v>18</v>
       </c>
       <c r="J137" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K137" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L137" s="11"/>
     </row>
-    <row r="138" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="10">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="F138" s="11" t="s">
         <v>50</v>
@@ -8419,28 +8418,28 @@
         <v>18</v>
       </c>
       <c r="J138" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K138" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L138" s="11"/>
     </row>
-    <row r="139" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A139" s="10">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="F139" s="11" t="s">
         <v>50</v>
@@ -8455,28 +8454,28 @@
         <v>18</v>
       </c>
       <c r="J139" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K139" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L139" s="11"/>
     </row>
-    <row r="140" spans="1:12" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="10">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="F140" s="11" t="s">
         <v>50</v>
@@ -8498,21 +8497,21 @@
       </c>
       <c r="L140" s="11"/>
     </row>
-    <row r="141" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A141" s="10">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="F141" s="11" t="s">
         <v>50</v>
@@ -8530,25 +8529,25 @@
         <v>18</v>
       </c>
       <c r="K141" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L141" s="11"/>
     </row>
-    <row r="142" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A142" s="10">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="F142" s="11" t="s">
         <v>50</v>
@@ -8566,25 +8565,25 @@
         <v>18</v>
       </c>
       <c r="K142" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L142" s="11"/>
     </row>
-    <row r="143" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="80" x14ac:dyDescent="0.2">
       <c r="A143" s="10">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="F143" s="11" t="s">
         <v>50</v>
@@ -8606,21 +8605,21 @@
       </c>
       <c r="L143" s="11"/>
     </row>
-    <row r="144" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A144" s="10">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="F144" s="11" t="s">
         <v>50</v>
@@ -8635,28 +8634,28 @@
         <v>18</v>
       </c>
       <c r="J144" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K144" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L144" s="11"/>
     </row>
-    <row r="145" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A145" s="10">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="F145" s="11" t="s">
         <v>50</v>
@@ -8678,24 +8677,24 @@
       </c>
       <c r="L145" s="11"/>
     </row>
-    <row r="146" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="10">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>120</v>
+        <v>279</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G146" s="10" t="s">
         <v>17</v>
@@ -8707,28 +8706,28 @@
         <v>18</v>
       </c>
       <c r="J146" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K146" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L146" s="11"/>
     </row>
-    <row r="147" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A147" s="10">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>189</v>
+        <v>281</v>
       </c>
       <c r="F147" s="11" t="s">
         <v>50</v>
@@ -8746,25 +8745,25 @@
         <v>18</v>
       </c>
       <c r="K147" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L147" s="11"/>
     </row>
-    <row r="148" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="10">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>189</v>
+        <v>283</v>
       </c>
       <c r="F148" s="11" t="s">
         <v>50</v>
@@ -8779,28 +8778,28 @@
         <v>18</v>
       </c>
       <c r="J148" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K148" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L148" s="11"/>
     </row>
-    <row r="149" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A149" s="10">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="F149" s="11" t="s">
         <v>50</v>
@@ -8822,21 +8821,21 @@
       </c>
       <c r="L149" s="11"/>
     </row>
-    <row r="150" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A150" s="10">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>48</v>
+        <v>286</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>189</v>
+        <v>287</v>
       </c>
       <c r="F150" s="11" t="s">
         <v>50</v>
@@ -8854,28 +8853,28 @@
         <v>18</v>
       </c>
       <c r="K150" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L150" s="11"/>
     </row>
-    <row r="151" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A151" s="10">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>120</v>
+        <v>288</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G151" s="10" t="s">
         <v>17</v>
@@ -8890,25 +8889,25 @@
         <v>18</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L151" s="11"/>
     </row>
-    <row r="152" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="10">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C152" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>48</v>
+        <v>289</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="F152" s="11" t="s">
         <v>50</v>
@@ -8926,25 +8925,25 @@
         <v>18</v>
       </c>
       <c r="K152" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L152" s="11"/>
     </row>
-    <row r="153" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A153" s="10">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="F153" s="11" t="s">
         <v>50</v>
@@ -8962,28 +8961,28 @@
         <v>18</v>
       </c>
       <c r="K153" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L153" s="11"/>
     </row>
-    <row r="154" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A154" s="10">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D154" s="7" t="s">
-        <v>120</v>
+        <v>293</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="G154" s="10" t="s">
         <v>17</v>
@@ -8998,25 +8997,25 @@
         <v>18</v>
       </c>
       <c r="K154" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L154" s="11"/>
     </row>
-    <row r="155" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="10">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="F155" s="11" t="s">
         <v>50</v>
@@ -9038,15 +9037,15 @@
       </c>
       <c r="L155" s="11"/>
     </row>
-    <row r="156" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="10">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>20</v>
@@ -9074,15 +9073,15 @@
       </c>
       <c r="L156" s="11"/>
     </row>
-    <row r="157" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="10">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>20</v>
@@ -9110,15 +9109,15 @@
       </c>
       <c r="L157" s="11"/>
     </row>
-    <row r="158" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="10">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>20</v>
@@ -9146,21 +9145,21 @@
       </c>
       <c r="L158" s="11"/>
     </row>
-    <row r="159" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="10">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F159" s="11" t="s">
         <v>50</v>
@@ -9182,21 +9181,21 @@
       </c>
       <c r="L159" s="11"/>
     </row>
-    <row r="160" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="10">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="D160" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>316</v>
+        <v>189</v>
       </c>
       <c r="F160" s="11" t="s">
         <v>50</v>
@@ -9218,21 +9217,21 @@
       </c>
       <c r="L160" s="11"/>
     </row>
-    <row r="161" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="10">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="F161" s="11" t="s">
         <v>50</v>
@@ -9247,28 +9246,28 @@
         <v>18</v>
       </c>
       <c r="J161" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K161" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L161" s="11"/>
     </row>
-    <row r="162" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="10">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>320</v>
+        <v>189</v>
       </c>
       <c r="F162" s="11" t="s">
         <v>50</v>
@@ -9283,28 +9282,28 @@
         <v>18</v>
       </c>
       <c r="J162" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K162" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L162" s="11"/>
     </row>
-    <row r="163" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="10">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>48</v>
+        <v>312</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F163" s="11" t="s">
         <v>50</v>
@@ -9326,21 +9325,21 @@
       </c>
       <c r="L163" s="11"/>
     </row>
-    <row r="164" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A164" s="10">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>48</v>
+        <v>315</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F164" s="11" t="s">
         <v>50</v>
@@ -9362,21 +9361,21 @@
       </c>
       <c r="L164" s="11"/>
     </row>
-    <row r="165" spans="1:12" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="10">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>48</v>
+        <v>317</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F165" s="11" t="s">
         <v>50</v>
@@ -9391,28 +9390,28 @@
         <v>18</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K165" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L165" s="11"/>
     </row>
-    <row r="166" spans="1:12" ht="16" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="10">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>216</v>
+        <v>314</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>48</v>
+        <v>319</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F166" s="11" t="s">
         <v>50</v>
@@ -9427,7 +9426,7 @@
         <v>18</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K166" s="10" t="s">
         <v>18</v>
@@ -9436,13 +9435,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L166" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="User Journey"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L166">
-      <sortCondition ref="A1:A166"/>
+      <sortCondition ref="D1:D166"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9542,7 +9536,7 @@
   <dimension ref="A1:M522"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="81.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
@@ -9556,7 +9550,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="40" t="s">
         <v>341</v>
       </c>
       <c r="B1" s="36"/>
@@ -9572,7 +9566,7 @@
       <c r="L1" s="36"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>342</v>
       </c>
       <c r="B2" s="36"/>
@@ -9588,7 +9582,7 @@
       <c r="L2" s="36"/>
     </row>
     <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="42" t="s">
         <v>343</v>
       </c>
       <c r="B4" s="36"/>
@@ -9604,7 +9598,7 @@
       <c r="L4" s="36"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="39" t="s">
         <v>344</v>
       </c>
       <c r="B6" s="36"/>
@@ -9684,7 +9678,7 @@
       <c r="L10" s="36"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="40" t="s">
+      <c r="A11" s="39" t="s">
         <v>349</v>
       </c>
       <c r="B11" s="36"/>
@@ -9700,7 +9694,7 @@
       <c r="L11" s="36"/>
     </row>
     <row r="13" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="42" t="s">
         <v>350</v>
       </c>
       <c r="B13" s="36"/>
@@ -9881,7 +9875,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="42" t="s">
         <v>368</v>
       </c>
       <c r="B31" s="36"/>
@@ -10137,7 +10131,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="42" t="s">
         <v>376</v>
       </c>
       <c r="B46" s="36"/>
@@ -10665,7 +10659,7 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="42" t="s">
         <v>437</v>
       </c>
       <c r="B65" s="36"/>
@@ -10681,7 +10675,7 @@
       <c r="L65" s="36"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A66" s="44" t="s">
+      <c r="A66" s="46" t="s">
         <v>438</v>
       </c>
       <c r="B66" s="36"/>
@@ -10697,7 +10691,7 @@
       <c r="L66" s="36"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="44" t="s">
         <v>439</v>
       </c>
       <c r="B68" s="36"/>
@@ -10713,7 +10707,7 @@
       <c r="L68" s="36"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="42" t="s">
+      <c r="A69" s="43" t="s">
         <v>440</v>
       </c>
       <c r="B69" s="36"/>
@@ -10729,7 +10723,7 @@
       <c r="L69" s="36"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" s="39" t="s">
+      <c r="A70" s="41" t="s">
         <v>441</v>
       </c>
       <c r="B70" s="36"/>
@@ -10745,7 +10739,7 @@
       <c r="L70" s="36"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="39" t="s">
+      <c r="A71" s="41" t="s">
         <v>442</v>
       </c>
       <c r="B71" s="36"/>
@@ -10761,7 +10755,7 @@
       <c r="L71" s="36"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" s="39" t="s">
+      <c r="A72" s="41" t="s">
         <v>443</v>
       </c>
       <c r="B72" s="36"/>
@@ -10777,7 +10771,7 @@
       <c r="L72" s="36"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" s="43" t="s">
+      <c r="A73" s="44" t="s">
         <v>444</v>
       </c>
       <c r="B73" s="36"/>
@@ -10793,7 +10787,7 @@
       <c r="L73" s="36"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" s="42" t="s">
+      <c r="A74" s="43" t="s">
         <v>445</v>
       </c>
       <c r="B74" s="36"/>
@@ -10809,7 +10803,7 @@
       <c r="L74" s="36"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="39" t="s">
+      <c r="A75" s="41" t="s">
         <v>446</v>
       </c>
       <c r="B75" s="36"/>
@@ -10825,7 +10819,7 @@
       <c r="L75" s="36"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A76" s="39" t="s">
+      <c r="A76" s="41" t="s">
         <v>447</v>
       </c>
       <c r="B76" s="36"/>
@@ -10841,7 +10835,7 @@
       <c r="L76" s="36"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" s="39" t="s">
+      <c r="A77" s="41" t="s">
         <v>448</v>
       </c>
       <c r="B77" s="36"/>
@@ -10857,7 +10851,7 @@
       <c r="L77" s="36"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="39" t="s">
+      <c r="A78" s="41" t="s">
         <v>449</v>
       </c>
       <c r="B78" s="36"/>
@@ -10873,7 +10867,7 @@
       <c r="L78" s="36"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="39" t="s">
+      <c r="A79" s="41" t="s">
         <v>450</v>
       </c>
       <c r="B79" s="36"/>
@@ -10889,7 +10883,7 @@
       <c r="L79" s="36"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80" s="39" t="s">
+      <c r="A80" s="41" t="s">
         <v>451</v>
       </c>
       <c r="B80" s="36"/>
@@ -10905,7 +10899,7 @@
       <c r="L80" s="36"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A81" s="39" t="s">
+      <c r="A81" s="41" t="s">
         <v>452</v>
       </c>
       <c r="B81" s="36"/>
@@ -10921,7 +10915,7 @@
       <c r="L81" s="36"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A82" s="39" t="s">
+      <c r="A82" s="41" t="s">
         <v>453</v>
       </c>
       <c r="B82" s="36"/>
@@ -10937,7 +10931,7 @@
       <c r="L82" s="36"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" s="38" t="s">
+      <c r="A83" s="37" t="s">
         <v>454</v>
       </c>
       <c r="B83" s="36"/>
@@ -10953,7 +10947,7 @@
       <c r="L83" s="36"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A84" s="38" t="s">
+      <c r="A84" s="37" t="s">
         <v>455</v>
       </c>
       <c r="B84" s="36"/>
@@ -10969,7 +10963,7 @@
       <c r="L84" s="36"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" s="38" t="s">
+      <c r="A85" s="37" t="s">
         <v>456</v>
       </c>
       <c r="B85" s="36"/>
@@ -10985,7 +10979,7 @@
       <c r="L85" s="36"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A86" s="42" t="s">
+      <c r="A86" s="43" t="s">
         <v>457</v>
       </c>
       <c r="B86" s="36"/>
@@ -11001,7 +10995,7 @@
       <c r="L86" s="36"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A87" s="39" t="s">
+      <c r="A87" s="41" t="s">
         <v>458</v>
       </c>
       <c r="B87" s="36"/>
@@ -11017,7 +11011,7 @@
       <c r="L87" s="36"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A88" s="37" t="s">
+      <c r="A88" s="38" t="s">
         <v>459</v>
       </c>
       <c r="B88" s="36"/>
@@ -11033,7 +11027,7 @@
       <c r="L88" s="36"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A89" s="38" t="s">
+      <c r="A89" s="37" t="s">
         <v>460</v>
       </c>
       <c r="B89" s="36"/>
@@ -11049,7 +11043,7 @@
       <c r="L89" s="36"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="38" t="s">
+      <c r="A90" s="37" t="s">
         <v>461</v>
       </c>
       <c r="B90" s="36"/>
@@ -11065,7 +11059,7 @@
       <c r="L90" s="36"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A91" s="43" t="s">
+      <c r="A91" s="44" t="s">
         <v>462</v>
       </c>
       <c r="B91" s="36"/>
@@ -11081,7 +11075,7 @@
       <c r="L91" s="36"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A92" s="42" t="s">
+      <c r="A92" s="43" t="s">
         <v>445</v>
       </c>
       <c r="B92" s="36"/>
@@ -11097,7 +11091,7 @@
       <c r="L92" s="36"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A93" s="39" t="s">
+      <c r="A93" s="41" t="s">
         <v>446</v>
       </c>
       <c r="B93" s="36"/>
@@ -11113,7 +11107,7 @@
       <c r="L93" s="36"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A94" s="39" t="s">
+      <c r="A94" s="41" t="s">
         <v>447</v>
       </c>
       <c r="B94" s="36"/>
@@ -11129,7 +11123,7 @@
       <c r="L94" s="36"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="39" t="s">
+      <c r="A95" s="41" t="s">
         <v>448</v>
       </c>
       <c r="B95" s="36"/>
@@ -11145,7 +11139,7 @@
       <c r="L95" s="36"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A96" s="39" t="s">
+      <c r="A96" s="41" t="s">
         <v>449</v>
       </c>
       <c r="B96" s="36"/>
@@ -11161,7 +11155,7 @@
       <c r="L96" s="36"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="39" t="s">
+      <c r="A97" s="41" t="s">
         <v>450</v>
       </c>
       <c r="B97" s="36"/>
@@ -11177,7 +11171,7 @@
       <c r="L97" s="36"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A98" s="39" t="s">
+      <c r="A98" s="41" t="s">
         <v>451</v>
       </c>
       <c r="B98" s="36"/>
@@ -11193,7 +11187,7 @@
       <c r="L98" s="36"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A99" s="39" t="s">
+      <c r="A99" s="41" t="s">
         <v>452</v>
       </c>
       <c r="B99" s="36"/>
@@ -11209,7 +11203,7 @@
       <c r="L99" s="36"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A100" s="39" t="s">
+      <c r="A100" s="41" t="s">
         <v>453</v>
       </c>
       <c r="B100" s="36"/>
@@ -11225,7 +11219,7 @@
       <c r="L100" s="36"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A101" s="38" t="s">
+      <c r="A101" s="37" t="s">
         <v>454</v>
       </c>
       <c r="B101" s="36"/>
@@ -11241,7 +11235,7 @@
       <c r="L101" s="36"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A102" s="38" t="s">
+      <c r="A102" s="37" t="s">
         <v>455</v>
       </c>
       <c r="B102" s="36"/>
@@ -11257,7 +11251,7 @@
       <c r="L102" s="36"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="37" t="s">
         <v>456</v>
       </c>
       <c r="B103" s="36"/>
@@ -11273,7 +11267,7 @@
       <c r="L103" s="36"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A104" s="42" t="s">
+      <c r="A104" s="43" t="s">
         <v>457</v>
       </c>
       <c r="B104" s="36"/>
@@ -11289,7 +11283,7 @@
       <c r="L104" s="36"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A105" s="39" t="s">
+      <c r="A105" s="41" t="s">
         <v>458</v>
       </c>
       <c r="B105" s="36"/>
@@ -11305,7 +11299,7 @@
       <c r="L105" s="36"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A106" s="37" t="s">
+      <c r="A106" s="38" t="s">
         <v>459</v>
       </c>
       <c r="B106" s="36"/>
@@ -11321,7 +11315,7 @@
       <c r="L106" s="36"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A107" s="38" t="s">
+      <c r="A107" s="37" t="s">
         <v>460</v>
       </c>
       <c r="B107" s="36"/>
@@ -11337,7 +11331,7 @@
       <c r="L107" s="36"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A108" s="38" t="s">
+      <c r="A108" s="37" t="s">
         <v>461</v>
       </c>
       <c r="B108" s="36"/>
@@ -11353,7 +11347,7 @@
       <c r="L108" s="36"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A109" s="42" t="s">
+      <c r="A109" s="43" t="s">
         <v>463</v>
       </c>
       <c r="B109" s="36"/>
@@ -11369,7 +11363,7 @@
       <c r="L109" s="36"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="39" t="s">
+      <c r="A110" s="41" t="s">
         <v>464</v>
       </c>
       <c r="B110" s="36"/>
@@ -11385,7 +11379,7 @@
       <c r="L110" s="36"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A111" s="39" t="s">
+      <c r="A111" s="41" t="s">
         <v>465</v>
       </c>
       <c r="B111" s="36"/>
@@ -11401,7 +11395,7 @@
       <c r="L111" s="36"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A112" s="37" t="s">
+      <c r="A112" s="38" t="s">
         <v>466</v>
       </c>
       <c r="B112" s="36"/>
@@ -11417,7 +11411,7 @@
       <c r="L112" s="36"/>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A113" s="37" t="s">
+      <c r="A113" s="38" t="s">
         <v>467</v>
       </c>
       <c r="B113" s="36"/>
@@ -11433,7 +11427,7 @@
       <c r="L113" s="36"/>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A114" s="42" t="s">
+      <c r="A114" s="43" t="s">
         <v>468</v>
       </c>
       <c r="B114" s="36"/>
@@ -11449,7 +11443,7 @@
       <c r="L114" s="36"/>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A115" s="39" t="s">
+      <c r="A115" s="41" t="s">
         <v>469</v>
       </c>
       <c r="B115" s="36"/>
@@ -11465,7 +11459,7 @@
       <c r="L115" s="36"/>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A116" s="38" t="s">
+      <c r="A116" s="37" t="s">
         <v>470</v>
       </c>
       <c r="B116" s="36"/>
@@ -11481,7 +11475,7 @@
       <c r="L116" s="36"/>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A117" s="38" t="s">
+      <c r="A117" s="37" t="s">
         <v>471</v>
       </c>
       <c r="B117" s="36"/>
@@ -11497,7 +11491,7 @@
       <c r="L117" s="36"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A118" s="46" t="s">
+      <c r="A118" s="47" t="s">
         <v>472</v>
       </c>
       <c r="B118" s="36"/>
@@ -11513,7 +11507,7 @@
       <c r="L118" s="36"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A119" s="42" t="s">
+      <c r="A119" s="43" t="s">
         <v>473</v>
       </c>
       <c r="B119" s="36"/>
@@ -11529,7 +11523,7 @@
       <c r="L119" s="36"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A120" s="39" t="s">
+      <c r="A120" s="41" t="s">
         <v>474</v>
       </c>
       <c r="B120" s="36"/>
@@ -11545,7 +11539,7 @@
       <c r="L120" s="36"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A121" s="39" t="s">
+      <c r="A121" s="41" t="s">
         <v>475</v>
       </c>
       <c r="B121" s="36"/>
@@ -11561,7 +11555,7 @@
       <c r="L121" s="36"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A122" s="38" t="s">
+      <c r="A122" s="37" t="s">
         <v>476</v>
       </c>
       <c r="B122" s="36"/>
@@ -11577,7 +11571,7 @@
       <c r="L122" s="36"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A123" s="42" t="s">
+      <c r="A123" s="43" t="s">
         <v>477</v>
       </c>
       <c r="B123" s="36"/>
@@ -11593,7 +11587,7 @@
       <c r="L123" s="36"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A124" s="39" t="s">
+      <c r="A124" s="41" t="s">
         <v>478</v>
       </c>
       <c r="B124" s="36"/>
@@ -11609,7 +11603,7 @@
       <c r="L124" s="36"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A125" s="37" t="s">
+      <c r="A125" s="38" t="s">
         <v>479</v>
       </c>
       <c r="B125" s="36"/>
@@ -11625,7 +11619,7 @@
       <c r="L125" s="36"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A126" s="38" t="s">
+      <c r="A126" s="37" t="s">
         <v>480</v>
       </c>
       <c r="B126" s="36"/>
@@ -11641,7 +11635,7 @@
       <c r="L126" s="36"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A127" s="38" t="s">
+      <c r="A127" s="37" t="s">
         <v>481</v>
       </c>
       <c r="B127" s="36"/>
@@ -11657,7 +11651,7 @@
       <c r="L127" s="36"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A128" s="38" t="s">
+      <c r="A128" s="37" t="s">
         <v>482</v>
       </c>
       <c r="B128" s="36"/>
@@ -11673,7 +11667,7 @@
       <c r="L128" s="36"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A129" s="38" t="s">
+      <c r="A129" s="37" t="s">
         <v>483</v>
       </c>
       <c r="B129" s="36"/>
@@ -11689,7 +11683,7 @@
       <c r="L129" s="36"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A130" s="42" t="s">
+      <c r="A130" s="43" t="s">
         <v>484</v>
       </c>
       <c r="B130" s="36"/>
@@ -11705,7 +11699,7 @@
       <c r="L130" s="36"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A131" s="39" t="s">
+      <c r="A131" s="41" t="s">
         <v>485</v>
       </c>
       <c r="B131" s="36"/>
@@ -11721,7 +11715,7 @@
       <c r="L131" s="36"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A132" s="37" t="s">
+      <c r="A132" s="38" t="s">
         <v>486</v>
       </c>
       <c r="B132" s="36"/>
@@ -11737,7 +11731,7 @@
       <c r="L132" s="36"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A133" s="37" t="s">
+      <c r="A133" s="38" t="s">
         <v>487</v>
       </c>
       <c r="B133" s="36"/>
@@ -11753,7 +11747,7 @@
       <c r="L133" s="36"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A134" s="37" t="s">
+      <c r="A134" s="38" t="s">
         <v>488</v>
       </c>
       <c r="B134" s="36"/>
@@ -11769,7 +11763,7 @@
       <c r="L134" s="36"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A135" s="38" t="s">
+      <c r="A135" s="37" t="s">
         <v>489</v>
       </c>
       <c r="B135" s="36"/>
@@ -11785,7 +11779,7 @@
       <c r="L135" s="36"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A136" s="42" t="s">
+      <c r="A136" s="43" t="s">
         <v>490</v>
       </c>
       <c r="B136" s="36"/>
@@ -11801,7 +11795,7 @@
       <c r="L136" s="36"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A137" s="39" t="s">
+      <c r="A137" s="41" t="s">
         <v>491</v>
       </c>
       <c r="B137" s="36"/>
@@ -11817,7 +11811,7 @@
       <c r="L137" s="36"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A138" s="37" t="s">
+      <c r="A138" s="38" t="s">
         <v>492</v>
       </c>
       <c r="B138" s="36"/>
@@ -11833,7 +11827,7 @@
       <c r="L138" s="36"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A139" s="37" t="s">
+      <c r="A139" s="38" t="s">
         <v>493</v>
       </c>
       <c r="B139" s="36"/>
@@ -11849,7 +11843,7 @@
       <c r="L139" s="36"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A140" s="37" t="s">
+      <c r="A140" s="38" t="s">
         <v>494</v>
       </c>
       <c r="B140" s="36"/>
@@ -11865,7 +11859,7 @@
       <c r="L140" s="36"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A141" s="37" t="s">
+      <c r="A141" s="38" t="s">
         <v>495</v>
       </c>
       <c r="B141" s="36"/>
@@ -11881,7 +11875,7 @@
       <c r="L141" s="36"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A142" s="38" t="s">
+      <c r="A142" s="37" t="s">
         <v>496</v>
       </c>
       <c r="B142" s="36"/>
@@ -11897,7 +11891,7 @@
       <c r="L142" s="36"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A143" s="38" t="s">
+      <c r="A143" s="37" t="s">
         <v>497</v>
       </c>
       <c r="B143" s="36"/>
@@ -11913,7 +11907,7 @@
       <c r="L143" s="36"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A144" s="38" t="s">
+      <c r="A144" s="37" t="s">
         <v>498</v>
       </c>
       <c r="B144" s="36"/>
@@ -11929,7 +11923,7 @@
       <c r="L144" s="36"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A145" s="42" t="s">
+      <c r="A145" s="43" t="s">
         <v>499</v>
       </c>
       <c r="B145" s="36"/>
@@ -11945,7 +11939,7 @@
       <c r="L145" s="36"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A146" s="39" t="s">
+      <c r="A146" s="41" t="s">
         <v>500</v>
       </c>
       <c r="B146" s="36"/>
@@ -11961,7 +11955,7 @@
       <c r="L146" s="36"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A147" s="42" t="s">
+      <c r="A147" s="43" t="s">
         <v>501</v>
       </c>
       <c r="B147" s="36"/>
@@ -11977,7 +11971,7 @@
       <c r="L147" s="36"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A148" s="39" t="s">
+      <c r="A148" s="41" t="s">
         <v>502</v>
       </c>
       <c r="B148" s="36"/>
@@ -11993,7 +11987,7 @@
       <c r="L148" s="36"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A149" s="37" t="s">
+      <c r="A149" s="38" t="s">
         <v>503</v>
       </c>
       <c r="B149" s="36"/>
@@ -12009,7 +12003,7 @@
       <c r="L149" s="36"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A150" s="37" t="s">
+      <c r="A150" s="38" t="s">
         <v>504</v>
       </c>
       <c r="B150" s="36"/>
@@ -12025,7 +12019,7 @@
       <c r="L150" s="36"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A151" s="37" t="s">
+      <c r="A151" s="38" t="s">
         <v>505</v>
       </c>
       <c r="B151" s="36"/>
@@ -12041,7 +12035,7 @@
       <c r="L151" s="36"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A152" s="37" t="s">
+      <c r="A152" s="38" t="s">
         <v>506</v>
       </c>
       <c r="B152" s="36"/>
@@ -12057,7 +12051,7 @@
       <c r="L152" s="36"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A153" s="37" t="s">
+      <c r="A153" s="38" t="s">
         <v>507</v>
       </c>
       <c r="B153" s="36"/>
@@ -12073,7 +12067,7 @@
       <c r="L153" s="36"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A154" s="37" t="s">
+      <c r="A154" s="38" t="s">
         <v>508</v>
       </c>
       <c r="B154" s="36"/>
@@ -12089,7 +12083,7 @@
       <c r="L154" s="36"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="37" t="s">
+      <c r="A155" s="38" t="s">
         <v>509</v>
       </c>
       <c r="B155" s="36"/>
@@ -12105,7 +12099,7 @@
       <c r="L155" s="36"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" s="37" t="s">
+      <c r="A156" s="38" t="s">
         <v>510</v>
       </c>
       <c r="B156" s="36"/>
@@ -12121,7 +12115,7 @@
       <c r="L156" s="36"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A157" s="37" t="s">
+      <c r="A157" s="38" t="s">
         <v>511</v>
       </c>
       <c r="B157" s="36"/>
@@ -12137,7 +12131,7 @@
       <c r="L157" s="36"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" s="37" t="s">
+      <c r="A158" s="38" t="s">
         <v>512</v>
       </c>
       <c r="B158" s="36"/>
@@ -12153,7 +12147,7 @@
       <c r="L158" s="36"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A159" s="37" t="s">
+      <c r="A159" s="38" t="s">
         <v>513</v>
       </c>
       <c r="B159" s="36"/>
@@ -12169,7 +12163,7 @@
       <c r="L159" s="36"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A160" s="37" t="s">
+      <c r="A160" s="38" t="s">
         <v>514</v>
       </c>
       <c r="B160" s="36"/>
@@ -12185,7 +12179,7 @@
       <c r="L160" s="36"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A161" s="37" t="s">
+      <c r="A161" s="38" t="s">
         <v>515</v>
       </c>
       <c r="B161" s="36"/>
@@ -12201,7 +12195,7 @@
       <c r="L161" s="36"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A162" s="37" t="s">
+      <c r="A162" s="38" t="s">
         <v>516</v>
       </c>
       <c r="B162" s="36"/>
@@ -12217,7 +12211,7 @@
       <c r="L162" s="36"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A163" s="38" t="s">
+      <c r="A163" s="37" t="s">
         <v>517</v>
       </c>
       <c r="B163" s="36"/>
@@ -12233,7 +12227,7 @@
       <c r="L163" s="36"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A164" s="38" t="s">
+      <c r="A164" s="37" t="s">
         <v>518</v>
       </c>
       <c r="B164" s="36"/>
@@ -12249,7 +12243,7 @@
       <c r="L164" s="36"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A165" s="38" t="s">
+      <c r="A165" s="37" t="s">
         <v>519</v>
       </c>
       <c r="B165" s="36"/>
@@ -12265,7 +12259,7 @@
       <c r="L165" s="36"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A166" s="38" t="s">
+      <c r="A166" s="37" t="s">
         <v>520</v>
       </c>
       <c r="B166" s="36"/>
@@ -12281,7 +12275,7 @@
       <c r="L166" s="36"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A167" s="38" t="s">
+      <c r="A167" s="37" t="s">
         <v>521</v>
       </c>
       <c r="B167" s="36"/>
@@ -12297,7 +12291,7 @@
       <c r="L167" s="36"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A168" s="38" t="s">
+      <c r="A168" s="37" t="s">
         <v>522</v>
       </c>
       <c r="B168" s="36"/>
@@ -12313,7 +12307,7 @@
       <c r="L168" s="36"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A169" s="38" t="s">
+      <c r="A169" s="37" t="s">
         <v>523</v>
       </c>
       <c r="B169" s="36"/>
@@ -12329,7 +12323,7 @@
       <c r="L169" s="36"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A170" s="38" t="s">
+      <c r="A170" s="37" t="s">
         <v>524</v>
       </c>
       <c r="B170" s="36"/>
@@ -12345,7 +12339,7 @@
       <c r="L170" s="36"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A171" s="38" t="s">
+      <c r="A171" s="37" t="s">
         <v>525</v>
       </c>
       <c r="B171" s="36"/>
@@ -12361,7 +12355,7 @@
       <c r="L171" s="36"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A172" s="38" t="s">
+      <c r="A172" s="37" t="s">
         <v>526</v>
       </c>
       <c r="B172" s="36"/>
@@ -12377,7 +12371,7 @@
       <c r="L172" s="36"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A173" s="38" t="s">
+      <c r="A173" s="37" t="s">
         <v>527</v>
       </c>
       <c r="B173" s="36"/>
@@ -12393,7 +12387,7 @@
       <c r="L173" s="36"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A174" s="46" t="s">
+      <c r="A174" s="47" t="s">
         <v>528</v>
       </c>
       <c r="B174" s="36"/>
@@ -12409,7 +12403,7 @@
       <c r="L174" s="36"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A175" s="42" t="s">
+      <c r="A175" s="43" t="s">
         <v>529</v>
       </c>
       <c r="B175" s="36"/>
@@ -12425,7 +12419,7 @@
       <c r="L175" s="36"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A176" s="39" t="s">
+      <c r="A176" s="41" t="s">
         <v>475</v>
       </c>
       <c r="B176" s="36"/>
@@ -12441,7 +12435,7 @@
       <c r="L176" s="36"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A177" s="37" t="s">
+      <c r="A177" s="38" t="s">
         <v>530</v>
       </c>
       <c r="B177" s="36"/>
@@ -12457,7 +12451,7 @@
       <c r="L177" s="36"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A178" s="38" t="s">
+      <c r="A178" s="37" t="s">
         <v>531</v>
       </c>
       <c r="B178" s="36"/>
@@ -12473,7 +12467,7 @@
       <c r="L178" s="36"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A179" s="43" t="s">
+      <c r="A179" s="44" t="s">
         <v>532</v>
       </c>
       <c r="B179" s="36"/>
@@ -12489,7 +12483,7 @@
       <c r="L179" s="36"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A180" s="42" t="s">
+      <c r="A180" s="43" t="s">
         <v>457</v>
       </c>
       <c r="B180" s="36"/>
@@ -12505,7 +12499,7 @@
       <c r="L180" s="36"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A181" s="39" t="s">
+      <c r="A181" s="41" t="s">
         <v>458</v>
       </c>
       <c r="B181" s="36"/>
@@ -12521,7 +12515,7 @@
       <c r="L181" s="36"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A182" s="37" t="s">
+      <c r="A182" s="38" t="s">
         <v>459</v>
       </c>
       <c r="B182" s="36"/>
@@ -12537,7 +12531,7 @@
       <c r="L182" s="36"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A183" s="38" t="s">
+      <c r="A183" s="37" t="s">
         <v>460</v>
       </c>
       <c r="B183" s="36"/>
@@ -12553,7 +12547,7 @@
       <c r="L183" s="36"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A184" s="38" t="s">
+      <c r="A184" s="37" t="s">
         <v>461</v>
       </c>
       <c r="B184" s="36"/>
@@ -12569,7 +12563,7 @@
       <c r="L184" s="36"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A185" s="42" t="s">
+      <c r="A185" s="43" t="s">
         <v>468</v>
       </c>
       <c r="B185" s="36"/>
@@ -12585,7 +12579,7 @@
       <c r="L185" s="36"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A186" s="39" t="s">
+      <c r="A186" s="41" t="s">
         <v>469</v>
       </c>
       <c r="B186" s="36"/>
@@ -12601,7 +12595,7 @@
       <c r="L186" s="36"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A187" s="38" t="s">
+      <c r="A187" s="37" t="s">
         <v>470</v>
       </c>
       <c r="B187" s="36"/>
@@ -12617,7 +12611,7 @@
       <c r="L187" s="36"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A188" s="38" t="s">
+      <c r="A188" s="37" t="s">
         <v>471</v>
       </c>
       <c r="B188" s="36"/>
@@ -12633,7 +12627,7 @@
       <c r="L188" s="36"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A189" s="46" t="s">
+      <c r="A189" s="47" t="s">
         <v>472</v>
       </c>
       <c r="B189" s="36"/>
@@ -12649,7 +12643,7 @@
       <c r="L189" s="36"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A190" s="42" t="s">
+      <c r="A190" s="43" t="s">
         <v>484</v>
       </c>
       <c r="B190" s="36"/>
@@ -12665,7 +12659,7 @@
       <c r="L190" s="36"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A191" s="39" t="s">
+      <c r="A191" s="41" t="s">
         <v>485</v>
       </c>
       <c r="B191" s="36"/>
@@ -12681,7 +12675,7 @@
       <c r="L191" s="36"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A192" s="37" t="s">
+      <c r="A192" s="38" t="s">
         <v>486</v>
       </c>
       <c r="B192" s="36"/>
@@ -12697,7 +12691,7 @@
       <c r="L192" s="36"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A193" s="37" t="s">
+      <c r="A193" s="38" t="s">
         <v>487</v>
       </c>
       <c r="B193" s="36"/>
@@ -12713,7 +12707,7 @@
       <c r="L193" s="36"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A194" s="37" t="s">
+      <c r="A194" s="38" t="s">
         <v>488</v>
       </c>
       <c r="B194" s="36"/>
@@ -12729,7 +12723,7 @@
       <c r="L194" s="36"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A195" s="38" t="s">
+      <c r="A195" s="37" t="s">
         <v>489</v>
       </c>
       <c r="B195" s="36"/>
@@ -12745,7 +12739,7 @@
       <c r="L195" s="36"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A196" s="42" t="s">
+      <c r="A196" s="43" t="s">
         <v>490</v>
       </c>
       <c r="B196" s="36"/>
@@ -12761,7 +12755,7 @@
       <c r="L196" s="36"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A197" s="39" t="s">
+      <c r="A197" s="41" t="s">
         <v>491</v>
       </c>
       <c r="B197" s="36"/>
@@ -12777,7 +12771,7 @@
       <c r="L197" s="36"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A198" s="37" t="s">
+      <c r="A198" s="38" t="s">
         <v>492</v>
       </c>
       <c r="B198" s="36"/>
@@ -12793,7 +12787,7 @@
       <c r="L198" s="36"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A199" s="37" t="s">
+      <c r="A199" s="38" t="s">
         <v>493</v>
       </c>
       <c r="B199" s="36"/>
@@ -12809,7 +12803,7 @@
       <c r="L199" s="36"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A200" s="37" t="s">
+      <c r="A200" s="38" t="s">
         <v>494</v>
       </c>
       <c r="B200" s="36"/>
@@ -12825,7 +12819,7 @@
       <c r="L200" s="36"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A201" s="37" t="s">
+      <c r="A201" s="38" t="s">
         <v>495</v>
       </c>
       <c r="B201" s="36"/>
@@ -12841,7 +12835,7 @@
       <c r="L201" s="36"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A202" s="38" t="s">
+      <c r="A202" s="37" t="s">
         <v>496</v>
       </c>
       <c r="B202" s="36"/>
@@ -12857,7 +12851,7 @@
       <c r="L202" s="36"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A203" s="38" t="s">
+      <c r="A203" s="37" t="s">
         <v>497</v>
       </c>
       <c r="B203" s="36"/>
@@ -12873,7 +12867,7 @@
       <c r="L203" s="36"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A204" s="38" t="s">
+      <c r="A204" s="37" t="s">
         <v>498</v>
       </c>
       <c r="B204" s="36"/>
@@ -12889,7 +12883,7 @@
       <c r="L204" s="36"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A205" s="42" t="s">
+      <c r="A205" s="43" t="s">
         <v>533</v>
       </c>
       <c r="B205" s="36"/>
@@ -12905,7 +12899,7 @@
       <c r="L205" s="36"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A206" s="39" t="s">
+      <c r="A206" s="41" t="s">
         <v>534</v>
       </c>
       <c r="B206" s="36"/>
@@ -12921,7 +12915,7 @@
       <c r="L206" s="36"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A207" s="37" t="s">
+      <c r="A207" s="38" t="s">
         <v>535</v>
       </c>
       <c r="B207" s="36"/>
@@ -12937,7 +12931,7 @@
       <c r="L207" s="36"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A208" s="37" t="s">
+      <c r="A208" s="38" t="s">
         <v>536</v>
       </c>
       <c r="B208" s="36"/>
@@ -12953,7 +12947,7 @@
       <c r="L208" s="36"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A209" s="42" t="s">
+      <c r="A209" s="43" t="s">
         <v>501</v>
       </c>
       <c r="B209" s="36"/>
@@ -12969,7 +12963,7 @@
       <c r="L209" s="36"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A210" s="39" t="s">
+      <c r="A210" s="41" t="s">
         <v>502</v>
       </c>
       <c r="B210" s="36"/>
@@ -12985,7 +12979,7 @@
       <c r="L210" s="36"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A211" s="37" t="s">
+      <c r="A211" s="38" t="s">
         <v>503</v>
       </c>
       <c r="B211" s="36"/>
@@ -13001,7 +12995,7 @@
       <c r="L211" s="36"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A212" s="37" t="s">
+      <c r="A212" s="38" t="s">
         <v>504</v>
       </c>
       <c r="B212" s="36"/>
@@ -13017,7 +13011,7 @@
       <c r="L212" s="36"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A213" s="37" t="s">
+      <c r="A213" s="38" t="s">
         <v>505</v>
       </c>
       <c r="B213" s="36"/>
@@ -13033,7 +13027,7 @@
       <c r="L213" s="36"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A214" s="37" t="s">
+      <c r="A214" s="38" t="s">
         <v>506</v>
       </c>
       <c r="B214" s="36"/>
@@ -13049,7 +13043,7 @@
       <c r="L214" s="36"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A215" s="37" t="s">
+      <c r="A215" s="38" t="s">
         <v>507</v>
       </c>
       <c r="B215" s="36"/>
@@ -13065,7 +13059,7 @@
       <c r="L215" s="36"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A216" s="37" t="s">
+      <c r="A216" s="38" t="s">
         <v>508</v>
       </c>
       <c r="B216" s="36"/>
@@ -13081,7 +13075,7 @@
       <c r="L216" s="36"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A217" s="37" t="s">
+      <c r="A217" s="38" t="s">
         <v>509</v>
       </c>
       <c r="B217" s="36"/>
@@ -13097,7 +13091,7 @@
       <c r="L217" s="36"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A218" s="37" t="s">
+      <c r="A218" s="38" t="s">
         <v>510</v>
       </c>
       <c r="B218" s="36"/>
@@ -13113,7 +13107,7 @@
       <c r="L218" s="36"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A219" s="37" t="s">
+      <c r="A219" s="38" t="s">
         <v>511</v>
       </c>
       <c r="B219" s="36"/>
@@ -13129,7 +13123,7 @@
       <c r="L219" s="36"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A220" s="37" t="s">
+      <c r="A220" s="38" t="s">
         <v>512</v>
       </c>
       <c r="B220" s="36"/>
@@ -13145,7 +13139,7 @@
       <c r="L220" s="36"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A221" s="37" t="s">
+      <c r="A221" s="38" t="s">
         <v>513</v>
       </c>
       <c r="B221" s="36"/>
@@ -13161,7 +13155,7 @@
       <c r="L221" s="36"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A222" s="37" t="s">
+      <c r="A222" s="38" t="s">
         <v>514</v>
       </c>
       <c r="B222" s="36"/>
@@ -13177,7 +13171,7 @@
       <c r="L222" s="36"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A223" s="37" t="s">
+      <c r="A223" s="38" t="s">
         <v>515</v>
       </c>
       <c r="B223" s="36"/>
@@ -13193,7 +13187,7 @@
       <c r="L223" s="36"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A224" s="37" t="s">
+      <c r="A224" s="38" t="s">
         <v>516</v>
       </c>
       <c r="B224" s="36"/>
@@ -13209,7 +13203,7 @@
       <c r="L224" s="36"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A225" s="38" t="s">
+      <c r="A225" s="37" t="s">
         <v>517</v>
       </c>
       <c r="B225" s="36"/>
@@ -13225,7 +13219,7 @@
       <c r="L225" s="36"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A226" s="38" t="s">
+      <c r="A226" s="37" t="s">
         <v>518</v>
       </c>
       <c r="B226" s="36"/>
@@ -13241,7 +13235,7 @@
       <c r="L226" s="36"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A227" s="38" t="s">
+      <c r="A227" s="37" t="s">
         <v>519</v>
       </c>
       <c r="B227" s="36"/>
@@ -13257,7 +13251,7 @@
       <c r="L227" s="36"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A228" s="38" t="s">
+      <c r="A228" s="37" t="s">
         <v>520</v>
       </c>
       <c r="B228" s="36"/>
@@ -13273,7 +13267,7 @@
       <c r="L228" s="36"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A229" s="38" t="s">
+      <c r="A229" s="37" t="s">
         <v>521</v>
       </c>
       <c r="B229" s="36"/>
@@ -13289,7 +13283,7 @@
       <c r="L229" s="36"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A230" s="38" t="s">
+      <c r="A230" s="37" t="s">
         <v>522</v>
       </c>
       <c r="B230" s="36"/>
@@ -13305,7 +13299,7 @@
       <c r="L230" s="36"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A231" s="38" t="s">
+      <c r="A231" s="37" t="s">
         <v>523</v>
       </c>
       <c r="B231" s="36"/>
@@ -13321,7 +13315,7 @@
       <c r="L231" s="36"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A232" s="38" t="s">
+      <c r="A232" s="37" t="s">
         <v>524</v>
       </c>
       <c r="B232" s="36"/>
@@ -13337,7 +13331,7 @@
       <c r="L232" s="36"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A233" s="38" t="s">
+      <c r="A233" s="37" t="s">
         <v>525</v>
       </c>
       <c r="B233" s="36"/>
@@ -13353,7 +13347,7 @@
       <c r="L233" s="36"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A234" s="38" t="s">
+      <c r="A234" s="37" t="s">
         <v>526</v>
       </c>
       <c r="B234" s="36"/>
@@ -13369,7 +13363,7 @@
       <c r="L234" s="36"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A235" s="38" t="s">
+      <c r="A235" s="37" t="s">
         <v>527</v>
       </c>
       <c r="B235" s="36"/>
@@ -13385,7 +13379,7 @@
       <c r="L235" s="36"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A236" s="46" t="s">
+      <c r="A236" s="47" t="s">
         <v>528</v>
       </c>
       <c r="B236" s="36"/>
@@ -13401,7 +13395,7 @@
       <c r="L236" s="36"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A237" s="42" t="s">
+      <c r="A237" s="43" t="s">
         <v>529</v>
       </c>
       <c r="B237" s="36"/>
@@ -13417,7 +13411,7 @@
       <c r="L237" s="36"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A238" s="39" t="s">
+      <c r="A238" s="41" t="s">
         <v>475</v>
       </c>
       <c r="B238" s="36"/>
@@ -13433,7 +13427,7 @@
       <c r="L238" s="36"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A239" s="37" t="s">
+      <c r="A239" s="38" t="s">
         <v>530</v>
       </c>
       <c r="B239" s="36"/>
@@ -13449,7 +13443,7 @@
       <c r="L239" s="36"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A240" s="38" t="s">
+      <c r="A240" s="37" t="s">
         <v>531</v>
       </c>
       <c r="B240" s="36"/>
@@ -13465,7 +13459,7 @@
       <c r="L240" s="36"/>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A241" s="42" t="s">
+      <c r="A241" s="43" t="s">
         <v>537</v>
       </c>
       <c r="B241" s="36"/>
@@ -13481,7 +13475,7 @@
       <c r="L241" s="36"/>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A242" s="39" t="s">
+      <c r="A242" s="41" t="s">
         <v>475</v>
       </c>
       <c r="B242" s="36"/>
@@ -13497,7 +13491,7 @@
       <c r="L242" s="36"/>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A243" s="37" t="s">
+      <c r="A243" s="38" t="s">
         <v>538</v>
       </c>
       <c r="B243" s="36"/>
@@ -13513,7 +13507,7 @@
       <c r="L243" s="36"/>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A244" s="43" t="s">
+      <c r="A244" s="44" t="s">
         <v>539</v>
       </c>
       <c r="B244" s="36"/>
@@ -13529,7 +13523,7 @@
       <c r="L244" s="36"/>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A245" s="42" t="s">
+      <c r="A245" s="43" t="s">
         <v>540</v>
       </c>
       <c r="B245" s="36"/>
@@ -13545,7 +13539,7 @@
       <c r="L245" s="36"/>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A246" s="39" t="s">
+      <c r="A246" s="41" t="s">
         <v>541</v>
       </c>
       <c r="B246" s="36"/>
@@ -13561,7 +13555,7 @@
       <c r="L246" s="36"/>
     </row>
     <row r="248" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="41" t="s">
+      <c r="A248" s="42" t="s">
         <v>542</v>
       </c>
       <c r="B248" s="36"/>
@@ -13577,7 +13571,7 @@
       <c r="L248" s="36"/>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A249" s="44" t="s">
+      <c r="A249" s="46" t="s">
         <v>543</v>
       </c>
       <c r="B249" s="36"/>
@@ -19415,7 +19409,7 @@
       </c>
     </row>
     <row r="418" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A418" s="41" t="s">
+      <c r="A418" s="42" t="s">
         <v>780</v>
       </c>
       <c r="B418" s="36"/>
@@ -19431,7 +19425,7 @@
       <c r="L418" s="36"/>
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A419" s="44" t="s">
+      <c r="A419" s="46" t="s">
         <v>781</v>
       </c>
       <c r="B419" s="36"/>
@@ -19830,7 +19824,7 @@
       </c>
     </row>
     <row r="445" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A445" s="41" t="s">
+      <c r="A445" s="42" t="s">
         <v>828</v>
       </c>
       <c r="B445" s="36"/>
@@ -19962,7 +19956,7 @@
       <c r="L456" s="36"/>
     </row>
     <row r="458" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A458" s="40" t="s">
+      <c r="A458" s="39" t="s">
         <v>846</v>
       </c>
       <c r="B458" s="36"/>
@@ -20156,7 +20150,7 @@
       </c>
     </row>
     <row r="474" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A474" s="41" t="s">
+      <c r="A474" s="42" t="s">
         <v>865</v>
       </c>
       <c r="B474" s="36"/>
@@ -20620,7 +20614,7 @@
       <c r="L495" s="36"/>
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A497" s="40" t="s">
+      <c r="A497" s="39" t="s">
         <v>882</v>
       </c>
       <c r="B497" s="36"/>
@@ -20941,6 +20935,211 @@
     </row>
   </sheetData>
   <mergeCells count="229">
+    <mergeCell ref="A128:L128"/>
+    <mergeCell ref="A193:L193"/>
+    <mergeCell ref="A137:L137"/>
+    <mergeCell ref="A497:L497"/>
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A208:L208"/>
+    <mergeCell ref="A89:L89"/>
+    <mergeCell ref="A136:L136"/>
+    <mergeCell ref="A192:L192"/>
+    <mergeCell ref="A105:L105"/>
+    <mergeCell ref="A145:L145"/>
+    <mergeCell ref="A139:L139"/>
+    <mergeCell ref="A113:L113"/>
+    <mergeCell ref="A210:L210"/>
+    <mergeCell ref="A179:L179"/>
+    <mergeCell ref="A71:L71"/>
+    <mergeCell ref="A129:L129"/>
+    <mergeCell ref="A185:L185"/>
+    <mergeCell ref="A194:L194"/>
+    <mergeCell ref="A203:L203"/>
+    <mergeCell ref="A234:L234"/>
+    <mergeCell ref="A114:L114"/>
+    <mergeCell ref="A98:L98"/>
+    <mergeCell ref="A191:L191"/>
+    <mergeCell ref="A169:L169"/>
+    <mergeCell ref="A107:L107"/>
+    <mergeCell ref="A178:L178"/>
+    <mergeCell ref="A476:L476"/>
+    <mergeCell ref="A181:L181"/>
+    <mergeCell ref="A91:L91"/>
+    <mergeCell ref="A184:L184"/>
+    <mergeCell ref="A131:L131"/>
+    <mergeCell ref="A100:L100"/>
+    <mergeCell ref="A156:L156"/>
+    <mergeCell ref="A171:L171"/>
+    <mergeCell ref="A460:L460"/>
+    <mergeCell ref="A165:L165"/>
+    <mergeCell ref="A115:L115"/>
+    <mergeCell ref="A155:L155"/>
+    <mergeCell ref="A93:L93"/>
+    <mergeCell ref="A220:L220"/>
+    <mergeCell ref="A102:L102"/>
+    <mergeCell ref="A173:L173"/>
+    <mergeCell ref="A229:L229"/>
+    <mergeCell ref="A130:L130"/>
+    <mergeCell ref="A222:L222"/>
+    <mergeCell ref="A520:L520"/>
+    <mergeCell ref="A138:L138"/>
+    <mergeCell ref="A132:L132"/>
+    <mergeCell ref="A238:L238"/>
+    <mergeCell ref="A456:L456"/>
+    <mergeCell ref="A474:L474"/>
+    <mergeCell ref="A513:L513"/>
+    <mergeCell ref="A506:L506"/>
+    <mergeCell ref="A249:L249"/>
+    <mergeCell ref="A176:L176"/>
+    <mergeCell ref="A143:L143"/>
+    <mergeCell ref="A245:L245"/>
+    <mergeCell ref="A507:L507"/>
+    <mergeCell ref="A218:L218"/>
+    <mergeCell ref="A499:L499"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A119:L119"/>
+    <mergeCell ref="A69:L69"/>
+    <mergeCell ref="A196:L196"/>
+    <mergeCell ref="A78:L78"/>
+    <mergeCell ref="A205:L205"/>
+    <mergeCell ref="A498:L498"/>
+    <mergeCell ref="A183:L183"/>
+    <mergeCell ref="A419:L419"/>
+    <mergeCell ref="A75:L75"/>
+    <mergeCell ref="A133:L133"/>
+    <mergeCell ref="A246:L246"/>
+    <mergeCell ref="A198:L198"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A233:L233"/>
+    <mergeCell ref="A84:L84"/>
+    <mergeCell ref="A66:L66"/>
+    <mergeCell ref="A236:L236"/>
+    <mergeCell ref="A118:L118"/>
+    <mergeCell ref="A149:L149"/>
+    <mergeCell ref="A189:L189"/>
+    <mergeCell ref="A447:L447"/>
+    <mergeCell ref="A158:L158"/>
+    <mergeCell ref="A223:L223"/>
+    <mergeCell ref="A522:L522"/>
+    <mergeCell ref="A418:L418"/>
+    <mergeCell ref="A120:L120"/>
+    <mergeCell ref="A239:L239"/>
+    <mergeCell ref="A95:L95"/>
+    <mergeCell ref="A248:L248"/>
+    <mergeCell ref="A515:L515"/>
+    <mergeCell ref="A104:L104"/>
+    <mergeCell ref="A175:L175"/>
+    <mergeCell ref="A235:L235"/>
+    <mergeCell ref="A159:L159"/>
+    <mergeCell ref="A97:L97"/>
+    <mergeCell ref="A219:L219"/>
+    <mergeCell ref="A514:L514"/>
+    <mergeCell ref="A106:L106"/>
+    <mergeCell ref="A200:L200"/>
+    <mergeCell ref="A509:L509"/>
+    <mergeCell ref="A462:L462"/>
+    <mergeCell ref="A511:L511"/>
+    <mergeCell ref="A172:L172"/>
+    <mergeCell ref="A187:L187"/>
+    <mergeCell ref="A221:L221"/>
+    <mergeCell ref="A174:L174"/>
+    <mergeCell ref="A108:L108"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A81:L81"/>
+    <mergeCell ref="A96:L96"/>
+    <mergeCell ref="A209:L209"/>
+    <mergeCell ref="A147:L147"/>
+    <mergeCell ref="A161:L161"/>
+    <mergeCell ref="A445:L445"/>
+    <mergeCell ref="A459:L459"/>
+    <mergeCell ref="A170:L170"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A202:L202"/>
+    <mergeCell ref="A211:L211"/>
+    <mergeCell ref="A186:L186"/>
+    <mergeCell ref="A73:L73"/>
+    <mergeCell ref="A201:L201"/>
+    <mergeCell ref="A226:L226"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="A123:L123"/>
+    <mergeCell ref="A197:L197"/>
+    <mergeCell ref="A110:L110"/>
+    <mergeCell ref="A146:L146"/>
+    <mergeCell ref="A228:L228"/>
+    <mergeCell ref="A124:L124"/>
+    <mergeCell ref="A237:L237"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A86:L86"/>
+    <mergeCell ref="A213:L213"/>
+    <mergeCell ref="A151:L151"/>
+    <mergeCell ref="A160:L160"/>
+    <mergeCell ref="A464:L464"/>
+    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A135:L135"/>
+    <mergeCell ref="A150:L150"/>
+    <mergeCell ref="A206:L206"/>
+    <mergeCell ref="A144:L144"/>
+    <mergeCell ref="A122:L122"/>
+    <mergeCell ref="A215:L215"/>
+    <mergeCell ref="A224:L224"/>
+    <mergeCell ref="A125:L125"/>
+    <mergeCell ref="A72:L72"/>
+    <mergeCell ref="A134:L134"/>
+    <mergeCell ref="A199:L199"/>
+    <mergeCell ref="A112:L112"/>
+    <mergeCell ref="A152:L152"/>
+    <mergeCell ref="A121:L121"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A127:L127"/>
+    <mergeCell ref="A167:L167"/>
+    <mergeCell ref="A70:L70"/>
+    <mergeCell ref="A241:L241"/>
+    <mergeCell ref="A153:L153"/>
+    <mergeCell ref="A162:L162"/>
+    <mergeCell ref="A517:L517"/>
+    <mergeCell ref="A227:L227"/>
+    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A177:L177"/>
+    <mergeCell ref="A90:L90"/>
+    <mergeCell ref="A212:L212"/>
+    <mergeCell ref="A243:L243"/>
+    <mergeCell ref="A217:L217"/>
+    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A164:L164"/>
+    <mergeCell ref="A501:L501"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A68:L68"/>
+    <mergeCell ref="A190:L190"/>
+    <mergeCell ref="A117:L117"/>
+    <mergeCell ref="A230:L230"/>
+    <mergeCell ref="A111:L111"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A77:L77"/>
+    <mergeCell ref="A512:L512"/>
+    <mergeCell ref="A101:L101"/>
+    <mergeCell ref="A242:L242"/>
+    <mergeCell ref="A195:L195"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="A204:L204"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A116:L116"/>
+    <mergeCell ref="A188:L188"/>
+    <mergeCell ref="A244:L244"/>
+    <mergeCell ref="A126:L126"/>
+    <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A109:L109"/>
+    <mergeCell ref="A231:L231"/>
+    <mergeCell ref="A180:L180"/>
+    <mergeCell ref="A495:L495"/>
+    <mergeCell ref="A240:L240"/>
+    <mergeCell ref="A504:L504"/>
+    <mergeCell ref="A88:L88"/>
+    <mergeCell ref="A83:L83"/>
+    <mergeCell ref="A148:L148"/>
+    <mergeCell ref="A92:L92"/>
+    <mergeCell ref="A157:L157"/>
+    <mergeCell ref="A166:L166"/>
     <mergeCell ref="A521:L521"/>
     <mergeCell ref="A232:L232"/>
     <mergeCell ref="A142:L142"/>
@@ -20965,211 +21164,6 @@
     <mergeCell ref="A503:L503"/>
     <mergeCell ref="A214:L214"/>
     <mergeCell ref="A163:L163"/>
-    <mergeCell ref="A512:L512"/>
-    <mergeCell ref="A101:L101"/>
-    <mergeCell ref="A242:L242"/>
-    <mergeCell ref="A195:L195"/>
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="A204:L204"/>
-    <mergeCell ref="A85:L85"/>
-    <mergeCell ref="A116:L116"/>
-    <mergeCell ref="A188:L188"/>
-    <mergeCell ref="A244:L244"/>
-    <mergeCell ref="A126:L126"/>
-    <mergeCell ref="A140:L140"/>
-    <mergeCell ref="A109:L109"/>
-    <mergeCell ref="A231:L231"/>
-    <mergeCell ref="A180:L180"/>
-    <mergeCell ref="A495:L495"/>
-    <mergeCell ref="A240:L240"/>
-    <mergeCell ref="A504:L504"/>
-    <mergeCell ref="A88:L88"/>
-    <mergeCell ref="A70:L70"/>
-    <mergeCell ref="A241:L241"/>
-    <mergeCell ref="A153:L153"/>
-    <mergeCell ref="A162:L162"/>
-    <mergeCell ref="A517:L517"/>
-    <mergeCell ref="A227:L227"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A177:L177"/>
-    <mergeCell ref="A90:L90"/>
-    <mergeCell ref="A212:L212"/>
-    <mergeCell ref="A243:L243"/>
-    <mergeCell ref="A217:L217"/>
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A164:L164"/>
-    <mergeCell ref="A501:L501"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A68:L68"/>
-    <mergeCell ref="A190:L190"/>
-    <mergeCell ref="A117:L117"/>
-    <mergeCell ref="A230:L230"/>
-    <mergeCell ref="A111:L111"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A86:L86"/>
-    <mergeCell ref="A213:L213"/>
-    <mergeCell ref="A151:L151"/>
-    <mergeCell ref="A160:L160"/>
-    <mergeCell ref="A464:L464"/>
-    <mergeCell ref="A141:L141"/>
-    <mergeCell ref="A135:L135"/>
-    <mergeCell ref="A150:L150"/>
-    <mergeCell ref="A206:L206"/>
-    <mergeCell ref="A144:L144"/>
-    <mergeCell ref="A122:L122"/>
-    <mergeCell ref="A215:L215"/>
-    <mergeCell ref="A224:L224"/>
-    <mergeCell ref="A125:L125"/>
-    <mergeCell ref="A72:L72"/>
-    <mergeCell ref="A134:L134"/>
-    <mergeCell ref="A199:L199"/>
-    <mergeCell ref="A112:L112"/>
-    <mergeCell ref="A152:L152"/>
-    <mergeCell ref="A121:L121"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A127:L127"/>
-    <mergeCell ref="A167:L167"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A81:L81"/>
-    <mergeCell ref="A96:L96"/>
-    <mergeCell ref="A209:L209"/>
-    <mergeCell ref="A147:L147"/>
-    <mergeCell ref="A161:L161"/>
-    <mergeCell ref="A445:L445"/>
-    <mergeCell ref="A459:L459"/>
-    <mergeCell ref="A170:L170"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A202:L202"/>
-    <mergeCell ref="A211:L211"/>
-    <mergeCell ref="A186:L186"/>
-    <mergeCell ref="A73:L73"/>
-    <mergeCell ref="A201:L201"/>
-    <mergeCell ref="A226:L226"/>
-    <mergeCell ref="A82:L82"/>
-    <mergeCell ref="A123:L123"/>
-    <mergeCell ref="A197:L197"/>
-    <mergeCell ref="A110:L110"/>
-    <mergeCell ref="A146:L146"/>
-    <mergeCell ref="A228:L228"/>
-    <mergeCell ref="A124:L124"/>
-    <mergeCell ref="A237:L237"/>
-    <mergeCell ref="A522:L522"/>
-    <mergeCell ref="A418:L418"/>
-    <mergeCell ref="A120:L120"/>
-    <mergeCell ref="A239:L239"/>
-    <mergeCell ref="A95:L95"/>
-    <mergeCell ref="A248:L248"/>
-    <mergeCell ref="A515:L515"/>
-    <mergeCell ref="A104:L104"/>
-    <mergeCell ref="A175:L175"/>
-    <mergeCell ref="A235:L235"/>
-    <mergeCell ref="A159:L159"/>
-    <mergeCell ref="A97:L97"/>
-    <mergeCell ref="A219:L219"/>
-    <mergeCell ref="A514:L514"/>
-    <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A200:L200"/>
-    <mergeCell ref="A509:L509"/>
-    <mergeCell ref="A462:L462"/>
-    <mergeCell ref="A511:L511"/>
-    <mergeCell ref="A172:L172"/>
-    <mergeCell ref="A187:L187"/>
-    <mergeCell ref="A221:L221"/>
-    <mergeCell ref="A174:L174"/>
-    <mergeCell ref="A108:L108"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A119:L119"/>
-    <mergeCell ref="A69:L69"/>
-    <mergeCell ref="A196:L196"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A205:L205"/>
-    <mergeCell ref="A498:L498"/>
-    <mergeCell ref="A183:L183"/>
-    <mergeCell ref="A419:L419"/>
-    <mergeCell ref="A75:L75"/>
-    <mergeCell ref="A133:L133"/>
-    <mergeCell ref="A246:L246"/>
-    <mergeCell ref="A198:L198"/>
-    <mergeCell ref="A80:L80"/>
-    <mergeCell ref="A233:L233"/>
-    <mergeCell ref="A84:L84"/>
-    <mergeCell ref="A66:L66"/>
-    <mergeCell ref="A236:L236"/>
-    <mergeCell ref="A118:L118"/>
-    <mergeCell ref="A149:L149"/>
-    <mergeCell ref="A189:L189"/>
-    <mergeCell ref="A447:L447"/>
-    <mergeCell ref="A158:L158"/>
-    <mergeCell ref="A223:L223"/>
-    <mergeCell ref="A77:L77"/>
-    <mergeCell ref="A83:L83"/>
-    <mergeCell ref="A148:L148"/>
-    <mergeCell ref="A92:L92"/>
-    <mergeCell ref="A157:L157"/>
-    <mergeCell ref="A166:L166"/>
-    <mergeCell ref="A222:L222"/>
-    <mergeCell ref="A520:L520"/>
-    <mergeCell ref="A138:L138"/>
-    <mergeCell ref="A132:L132"/>
-    <mergeCell ref="A238:L238"/>
-    <mergeCell ref="A456:L456"/>
-    <mergeCell ref="A474:L474"/>
-    <mergeCell ref="A513:L513"/>
-    <mergeCell ref="A506:L506"/>
-    <mergeCell ref="A249:L249"/>
-    <mergeCell ref="A176:L176"/>
-    <mergeCell ref="A114:L114"/>
-    <mergeCell ref="A98:L98"/>
-    <mergeCell ref="A191:L191"/>
-    <mergeCell ref="A169:L169"/>
-    <mergeCell ref="A107:L107"/>
-    <mergeCell ref="A178:L178"/>
-    <mergeCell ref="A476:L476"/>
-    <mergeCell ref="A181:L181"/>
-    <mergeCell ref="A91:L91"/>
-    <mergeCell ref="A184:L184"/>
-    <mergeCell ref="A131:L131"/>
-    <mergeCell ref="A100:L100"/>
-    <mergeCell ref="A156:L156"/>
-    <mergeCell ref="A171:L171"/>
-    <mergeCell ref="A460:L460"/>
-    <mergeCell ref="A165:L165"/>
-    <mergeCell ref="A115:L115"/>
-    <mergeCell ref="A155:L155"/>
-    <mergeCell ref="A93:L93"/>
-    <mergeCell ref="A220:L220"/>
-    <mergeCell ref="A102:L102"/>
-    <mergeCell ref="A173:L173"/>
-    <mergeCell ref="A229:L229"/>
-    <mergeCell ref="A130:L130"/>
-    <mergeCell ref="A143:L143"/>
-    <mergeCell ref="A245:L245"/>
-    <mergeCell ref="A507:L507"/>
-    <mergeCell ref="A218:L218"/>
-    <mergeCell ref="A128:L128"/>
-    <mergeCell ref="A193:L193"/>
-    <mergeCell ref="A137:L137"/>
-    <mergeCell ref="A497:L497"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A208:L208"/>
-    <mergeCell ref="A89:L89"/>
-    <mergeCell ref="A136:L136"/>
-    <mergeCell ref="A192:L192"/>
-    <mergeCell ref="A105:L105"/>
-    <mergeCell ref="A145:L145"/>
-    <mergeCell ref="A139:L139"/>
-    <mergeCell ref="A113:L113"/>
-    <mergeCell ref="A210:L210"/>
-    <mergeCell ref="A499:L499"/>
-    <mergeCell ref="A179:L179"/>
-    <mergeCell ref="A71:L71"/>
-    <mergeCell ref="A129:L129"/>
-    <mergeCell ref="A185:L185"/>
-    <mergeCell ref="A194:L194"/>
-    <mergeCell ref="A203:L203"/>
-    <mergeCell ref="A234:L234"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
